--- a/TestData/TMTT0035666_VerifyInternalDealTeamForAnalystRoleLimitForFRLOBOpportunityEngagement.xlsx
+++ b/TestData/TMTT0035666_VerifyInternalDealTeamForAnalystRoleLimitForFRLOBOpportunityEngagement.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vijay.kumar\source\repos\SalesForce_Project\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VKumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{276C3E63-AA61-43FD-B168-834562EB5199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1817BCE7-3125-429E-8651-880E18FE4651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28950" windowHeight="14610" activeTab="3" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="139">
   <si>
     <t>Client</t>
   </si>
@@ -266,9 +266,6 @@
     <t>Preston Wolf</t>
   </si>
   <si>
-    <t>Rich Bowman</t>
-  </si>
-  <si>
     <t>Rittik Chakrabarti</t>
   </si>
   <si>
@@ -368,19 +365,10 @@
     <t>Akshat Jamad</t>
   </si>
   <si>
-    <t>Alan Frederick Hall</t>
-  </si>
-  <si>
     <t>Alberico Altieri</t>
   </si>
   <si>
-    <t>Alberto Alonso Basagoiti</t>
-  </si>
-  <si>
     <t>Albert Sung</t>
-  </si>
-  <si>
-    <t>Alejandro Arturo Serrano Leo</t>
   </si>
   <si>
     <t>Aleksandra Chadam</t>
@@ -849,22 +837,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11A698FC-E7B6-4C83-A074-4EAE7093E960}">
   <dimension ref="A1:AF2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -941,7 +929,7 @@
         <v>24</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>25</v>
@@ -953,7 +941,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -961,7 +949,7 @@
         <v>28</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D2" t="s">
         <v>29</v>
@@ -994,16 +982,16 @@
         <v>35</v>
       </c>
       <c r="N2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="R2" t="s">
         <v>36</v>
@@ -1012,7 +1000,7 @@
         <v>36</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="U2" t="s">
         <v>37</v>
@@ -1027,19 +1015,19 @@
         <v>40</v>
       </c>
       <c r="Y2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="Z2" t="s">
         <v>41</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="AC2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AD2" t="s">
         <v>31</v>
@@ -1048,7 +1036,7 @@
         <v>31</v>
       </c>
       <c r="AF2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -1059,13 +1047,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{398AFF69-DCD2-4291-899D-46D247625F33}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>42</v>
       </c>
@@ -1073,12 +1061,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -1089,9 +1077,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{157DEAB0-0FBE-44C7-9D14-EA88B9DE7C90}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1117,7 +1105,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -1151,318 +1139,315 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53E8CB76-FB8A-4028-8972-B88CE86EF1D8}">
   <dimension ref="A1:D53"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" customWidth="1"/>
-    <col min="4" max="4" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>60</v>
       </c>
       <c r="D5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>61</v>
       </c>
       <c r="D6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>62</v>
       </c>
       <c r="D7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>63</v>
       </c>
       <c r="D8" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>65</v>
       </c>
       <c r="D10" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>66</v>
       </c>
       <c r="D11" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>67</v>
       </c>
       <c r="D12" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>68</v>
       </c>
-      <c r="D13" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>69</v>
       </c>
       <c r="D14" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>70</v>
       </c>
       <c r="D15" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
         <v>114</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" s="1" t="s">
-        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -1473,37 +1458,37 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C94118-6319-40E3-9C0E-6605217BB92A}">
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B2">
         <v>65</v>
       </c>
       <c r="H2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I2">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B3">
         <v>65</v>
@@ -1517,24 +1502,24 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6F88B60-A419-401F-AD7F-AECB9C160562}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -1545,34 +1530,34 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41831907-90E4-4F72-A4FC-60E82CC27F92}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="76.21875" customWidth="1"/>
-    <col min="2" max="2" width="18.109375" customWidth="1"/>
+    <col min="1" max="1" width="76.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
-        <v>87</v>
-      </c>
       <c r="B2" s="3" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/TMTT0035666_VerifyInternalDealTeamForAnalystRoleLimitForFRLOBOpportunityEngagement.xlsx
+++ b/TestData/TMTT0035666_VerifyInternalDealTeamForAnalystRoleLimitForFRLOBOpportunityEngagement.xlsx
@@ -1,25 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VKumar0427\source\repos\SF_Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1817BCE7-3125-429E-8651-880E18FE4651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C7187C4-295F-493B-8F50-0D0FF446CA12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28950" windowHeight="14610" activeTab="3" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
     <sheet name="Users" sheetId="2" r:id="rId2"/>
-    <sheet name="AddContact" sheetId="3" r:id="rId3"/>
-    <sheet name="OppDealTeamMembers" sheetId="4" r:id="rId4"/>
-    <sheet name="Roles" sheetId="7" r:id="rId5"/>
-    <sheet name="EngDealTeamMembers" sheetId="5" r:id="rId6"/>
-    <sheet name="OverlimitMessage" sheetId="6" r:id="rId7"/>
+    <sheet name="AppName" sheetId="8" r:id="rId3"/>
+    <sheet name="ModuleName" sheetId="9" r:id="rId4"/>
+    <sheet name="AddContact" sheetId="3" r:id="rId5"/>
+    <sheet name="OppDealTeamMembers" sheetId="4" r:id="rId6"/>
+    <sheet name="Roles" sheetId="7" r:id="rId7"/>
+    <sheet name="EngDealTeamMembers" sheetId="5" r:id="rId8"/>
+    <sheet name="OverlimitMessage" sheetId="6" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="145">
   <si>
     <t>Client</t>
   </si>
@@ -125,9 +127,6 @@
     <t>Fee</t>
   </si>
   <si>
-    <t>WomenLed</t>
-  </si>
-  <si>
     <t>Techno Coatings, Inc.</t>
   </si>
   <si>
@@ -143,9 +142,6 @@
     <t>Accountant</t>
   </si>
   <si>
-    <t>AM</t>
-  </si>
-  <si>
     <t>HL Capital, Inc.</t>
   </si>
   <si>
@@ -434,12 +430,6 @@
     <t>52</t>
   </si>
   <si>
-    <t>10.0</t>
-  </si>
-  <si>
-    <t>9999.0</t>
-  </si>
-  <si>
     <t>Creditor Advisors</t>
   </si>
   <si>
@@ -452,13 +442,43 @@
     <t>FR</t>
   </si>
   <si>
-    <t>FRJobType</t>
-  </si>
-  <si>
     <t>10000</t>
   </si>
   <si>
     <t>Africa</t>
+  </si>
+  <si>
+    <t>App Name</t>
+  </si>
+  <si>
+    <t>HL Banker</t>
+  </si>
+  <si>
+    <t>Module Name</t>
+  </si>
+  <si>
+    <t>Opportunities</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>9999</t>
+  </si>
+  <si>
+    <t>FASJobType</t>
+  </si>
+  <si>
+    <t>EMEAInitiatives</t>
+  </si>
+  <si>
+    <t>LegalAdvisorComp</t>
+  </si>
+  <si>
+    <t>LegalAdvisorHL</t>
+  </si>
+  <si>
+    <t>LA</t>
   </si>
 </sst>
 </file>
@@ -929,7 +949,7 @@
         <v>24</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>25</v>
@@ -937,106 +957,115 @@
       <c r="AB1" s="1" t="s">
         <v>26</v>
       </c>
+      <c r="AC1" s="1" t="s">
+        <v>141</v>
+      </c>
       <c r="AD1" s="1" t="s">
-        <v>27</v>
+        <v>142</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="D2" t="s">
         <v>28</v>
       </c>
-      <c r="B2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" s="6" t="s">
+      <c r="E2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2" t="s">
+        <v>144</v>
+      </c>
+      <c r="L2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N2" t="s">
+        <v>129</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="R2" t="s">
+        <v>34</v>
+      </c>
+      <c r="S2" t="s">
+        <v>34</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="U2" t="s">
+        <v>35</v>
+      </c>
+      <c r="V2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W2" t="s">
+        <v>37</v>
+      </c>
+      <c r="X2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>131</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="AB2" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="AC2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AD2" t="s">
         <v>30</v>
       </c>
-      <c r="F2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" t="s">
-        <v>31</v>
-      </c>
-      <c r="J2" t="s">
-        <v>31</v>
-      </c>
-      <c r="K2" t="s">
-        <v>33</v>
-      </c>
-      <c r="L2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N2" t="s">
-        <v>133</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="R2" t="s">
-        <v>36</v>
-      </c>
-      <c r="S2" t="s">
-        <v>36</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="U2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V2" t="s">
-        <v>38</v>
-      </c>
-      <c r="W2" t="s">
-        <v>39</v>
-      </c>
-      <c r="X2" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>135</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>138</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>31</v>
-      </c>
       <c r="AE2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AF2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -1055,18 +1084,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -1075,60 +1104,100 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86829626-F719-4BD0-AEC4-F096FBF467CD}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B9CE0B9-361D-4D21-9EAF-7162B1BF1310}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{157DEAB0-0FBE-44C7-9D14-EA88B9DE7C90}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" t="s">
         <v>52</v>
-      </c>
-      <c r="C2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" t="s">
-        <v>54</v>
       </c>
       <c r="E2" t="s">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1136,7 +1205,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53E8CB76-FB8A-4028-8972-B88CE86EF1D8}">
   <dimension ref="A1:D53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1148,306 +1217,306 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D12" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D14" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -1455,7 +1524,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C94118-6319-40E3-9C0E-6605217BB92A}">
   <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1466,21 +1535,21 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B2">
         <v>65</v>
       </c>
       <c r="H2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I2">
         <v>25</v>
@@ -1488,7 +1557,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B3">
         <v>65</v>
@@ -1499,7 +1568,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6F88B60-A419-401F-AD7F-AECB9C160562}">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1509,17 +1578,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -1527,7 +1596,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41831907-90E4-4F72-A4FC-60E82CC27F92}">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1538,26 +1607,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
